--- a/public/templates/examples/A-160-VulnerabilityScanningSchedule-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-160-VulnerabilityScanningSchedule-EXAMPLE-M.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Schedule!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -195,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -260,6 +265,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,7 +658,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="9" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -762,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Automated vulnerability scan</t>
@@ -788,18 +800,14 @@
           <t>Security Coordinator</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+      <c r="F11" s="26">
+        <v>46201</v>
+      </c>
+      <c r="G11" s="28">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Authenticated / credentialed scan</t>
@@ -825,18 +833,14 @@
           <t>Security Coordinator</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="F12" s="26">
+        <v>46201</v>
+      </c>
+      <c r="G12" s="28">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Penetration test (independent assessor)</t>
@@ -862,18 +866,14 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="F13" s="26">
+        <v>45920</v>
+      </c>
+      <c r="G13" s="28">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Independent control assessment</t>
@@ -899,15 +899,11 @@
           <t>Security Coordinator</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
+      <c r="F14" s="26">
+        <v>45920</v>
+      </c>
+      <c r="G14" s="28">
+        <v>46141</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
@@ -968,7 +964,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-04-30)</t>
         </is>
       </c>
     </row>
@@ -981,7 +977,6 @@
       <c r="B23" s="25" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -992,8 +987,7 @@
       </c>
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
-        <f>COUNTIF(G11:G20,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(G11:G20,"&lt;"&amp;DATE(2026,4,30))</f>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1012,7 +1006,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="9" t="n"/>
     </row>
-    <row r="29" ht="48" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scan or assessment is past due, the Security Coordinator is notified and the item is completed or rescheduled within 5 business days. Findings from every scan and assessment are recorded in the Vulnerability Assessment Reports and tracked to closure in the Risk / Finding Register.</t>
@@ -1099,10 +1093,8 @@
           <t>/s/ Dana Mercer</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="D41" s="27">
+        <v>46037</v>
       </c>
       <c r="E41" s="15" t="n"/>
       <c r="F41" s="15" t="n"/>
@@ -1123,10 +1115,8 @@
           <t>/s/ Anthony Reyes</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="D42" s="27">
+        <v>46037</v>
       </c>
       <c r="E42" s="15" t="n"/>
       <c r="F42" s="15" t="n"/>
@@ -1163,16 +1153,14 @@
       <c r="E45" s="14" t="n"/>
       <c r="F45" s="14" t="n"/>
     </row>
-    <row r="46" ht="17" customHeight="1">
+    <row r="46" ht="34.7" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="B46" s="26">
+        <v>46037</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
@@ -1188,11 +1176,11 @@
       <c r="F46" s="12" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:G6"/>
@@ -1210,7 +1198,6 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
@@ -1222,14 +1209,8 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F11:F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"On track,Due soon,Overdue,Complete"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>